--- a/resources/templates/ap_payment_opening/英雄期初对公付款单导入模版.xlsx
+++ b/resources/templates/ap_payment_opening/英雄期初对公付款单导入模版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9105"/>
+    <workbookView windowWidth="27690" windowHeight="16425"/>
   </bookViews>
   <sheets>
     <sheet name="期初对公付款单导入" sheetId="5" r:id="rId1"/>
@@ -30,7 +30,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+  <si>
+    <t>当前节点</t>
+  </si>
+  <si>
+    <t>当前状况</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -326,6 +332,12 @@
     </font>
     <font>
       <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color indexed="8"/>
       <name val="楷体"/>
       <charset val="134"/>
@@ -334,12 +346,6 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -970,7 +976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -980,28 +986,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -1350,29 +1359,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.85"/>
+  <dimension ref="A1:Z11"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.8318584070796" style="2" customWidth="1"/>
-    <col min="2" max="3" width="16.3362831858407" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.3362831858407" style="2" customWidth="1"/>
-    <col min="5" max="6" width="13.8318584070796" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.3362831858407" style="2" customWidth="1"/>
-    <col min="9" max="10" width="16.3362831858407" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.66371681415929" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.8318584070796" style="2"/>
-    <col min="13" max="13" width="19" style="2" customWidth="1"/>
-    <col min="14" max="15" width="13.8318584070796" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.8318584070796" style="2"/>
-    <col min="17" max="21" width="16.3362831858407" style="2" customWidth="1"/>
-    <col min="22" max="22" width="13.8318584070796" style="2" customWidth="1"/>
-    <col min="23" max="23" width="19" style="2" customWidth="1"/>
-    <col min="24" max="24" width="29.3362831858407" style="2" customWidth="1"/>
-    <col min="25" max="25" width="18.8849557522124" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="10.8318584070796" style="2"/>
+    <col min="1" max="2" width="11" style="2"/>
+    <col min="3" max="3" width="11.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="5" width="16.3333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.3333333333333" style="2" customWidth="1"/>
+    <col min="7" max="8" width="13.8333333333333" style="2" customWidth="1"/>
+    <col min="9" max="10" width="11.3333333333333" style="2" customWidth="1"/>
+    <col min="11" max="12" width="16.3333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.66666666666667" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.8333333333333" style="2"/>
+    <col min="15" max="15" width="19" style="2" customWidth="1"/>
+    <col min="16" max="17" width="13.8333333333333" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.8333333333333" style="2"/>
+    <col min="19" max="23" width="16.3333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="13.8333333333333" style="2" customWidth="1"/>
+    <col min="25" max="25" width="19" style="2" customWidth="1"/>
+    <col min="26" max="26" width="29.3333333333333" style="2" customWidth="1"/>
+    <col min="27" max="27" width="18.8833333333333" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="10.8333333333333" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17.65" spans="1:24">
+    <row r="1" s="1" customFormat="1" ht="18.75" spans="1:26">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1382,25 +1392,25 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
@@ -1415,117 +1425,123 @@
       <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+    <row r="2" spans="1:26">
+      <c r="C2" s="12"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
     </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+    <row r="3" spans="1:26">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
     </row>
-    <row r="7" spans="1:24">
-      <c r="B7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="13"/>
+    <row r="7" spans="1:26">
+      <c r="D7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:24">
-      <c r="B8" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="13"/>
+    <row r="8" spans="1:26">
+      <c r="D8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="14"/>
     </row>
-    <row r="9" spans="1:24">
-      <c r="B9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="13"/>
+    <row r="9" spans="1:26">
+      <c r="D9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:24">
-      <c r="B10" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="13"/>
+    <row r="10" spans="1:26">
+      <c r="D10" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="14"/>
     </row>
-    <row r="11" spans="1:24">
-      <c r="B11" s="13" t="s">
-        <v>28</v>
+    <row r="11" spans="1:26">
+      <c r="D11" s="14" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="23">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，不填下默认当天，填写下，格式需为yyyy-mm-dd" sqref="Q1"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="费用项目编码-&gt;[费用项目定义]中台费用项目编码" sqref="T1 S2:T1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="默认为：FW" sqref="A$1:A$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="oa原单号" sqref="B$1:B$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="不填写，默认当日，如填写，限制格式为yyyy-mm-dd" sqref="C$1:C$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="默认为：AP01-1" sqref="D$1:D$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="数据填写说明" prompt="申请人员工工号-&gt;[员工定义]下中台员工工号" sqref="E$1:E$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入申请人工号。" sqref="F$1:F$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="订单编号-&gt;[订单主数据查询]下中台订单编号" sqref="G$1:G$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 订单编码" sqref="H$1:H$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="核算主体编码-&gt;[核算架构管理&gt;核算主体]中台核算主体编码" sqref="I$1:I$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 核算主体编码" sqref="J$1:J$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="限制150字" sqref="K$1:K$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="预付款金额（支付币种）超1万人民币，必填" sqref="L$1:L$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="存在收支计划行的合同则必填" sqref="M$1:M$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="收款方编码-&gt;[供应商主数据查询]中台供应商编码" sqref="N$1:N$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值，收款方编码" sqref="O$1:O$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="未填写下，匹配收款方在供应商主数据库默认银行账号。填写下，根据填写内容校验供应商主数据库中存在此银行账号" sqref="P$1:P$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="限制100字" sqref="R$1:R$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 费用项目编码" sqref="U$1:U$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="主播卡片-&gt;[主播卡片主数据查询&gt;平台信息]房间号" sqref="V$1:V$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="国际币种编码，如人民币 CNY，美元 USD" sqref="W$1:W$1048576"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="最多2位小数" sqref="X$1:X$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，不填下默认当天，填写下，格式需为yyyy-mm-dd" sqref="S1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="费用项目编码-&gt;[费用项目定义]中台费用项目编码" sqref="V1 U2:V1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="默认为：FW" sqref="C$1:C$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="oa原单号" sqref="D$1:D$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="不填写，默认当日，如填写，限制格式为yyyy-mm-dd" sqref="E$1:E$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="默认为：AP01-1" sqref="F$1:F$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="数据填写说明" prompt="申请人员工工号-&gt;[员工定义]下中台员工工号" sqref="G$1:G$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入申请人工号。" sqref="H$1:H$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="订单编号-&gt;[订单主数据查询]下中台订单编号" sqref="I$1:I$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 订单编码" sqref="J$1:J$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="核算主体编码-&gt;[核算架构管理&gt;核算主体]中台核算主体编码" sqref="K$1:K$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 核算主体编码" sqref="L$1:L$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="限制150字" sqref="M$1:M$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="预付款金额（支付币种）超1万人民币，必填" sqref="N$1:N$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="存在收支计划行的合同则必填" sqref="O$1:O$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="收款方编码-&gt;[供应商主数据查询]中台供应商编码" sqref="P$1:P$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值，收款方编码" sqref="Q$1:Q$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="未填写下，匹配收款方在供应商主数据库默认银行账号。填写下，根据填写内容校验供应商主数据库中存在此银行账号" sqref="R$1:R$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="限制100字" sqref="T$1:T$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="可不填，系统实际存入值 费用项目编码" sqref="W$1:W$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="主播卡片-&gt;[主播卡片主数据查询&gt;平台信息]房间号" sqref="X$1:X$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="国际币种编码，如人民币 CNY，美元 USD" sqref="Y$1:Y$1048576"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="填写说明" prompt="最多2位小数" sqref="Z$1:Z$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1537,16 +1553,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.83185840707965" defaultRowHeight="13.85" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1559,16 +1575,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.83185840707965" defaultRowHeight="13.85" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1581,21 +1597,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="8.83185840707965" defaultRowHeight="13.85" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
